--- a/Design/Configs/Localization/MultilingualConfigs.xlsx
+++ b/Design/Configs/Localization/MultilingualConfigs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dudu502\LittleBee\Design\Configs\Localization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GraduationProject\mylockedstep\Design\Configs\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7BBB3C-43FF-4884-89BB-CA7B88C30D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7728CF4-08F2-446C-B384-493E7363E8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="104">
   <si>
     <t>Key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -313,10 +313,6 @@
   </si>
   <si>
     <t>警告</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>播放</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -762,14 +758,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C52"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="84.125" customWidth="1"/>
-    <col min="2" max="2" width="62.5" customWidth="1"/>
-    <col min="3" max="3" width="43.625" customWidth="1"/>
+    <col min="1" max="1" width="84.109375" customWidth="1"/>
+    <col min="2" max="2" width="62.44140625" customWidth="1"/>
+    <col min="3" max="3" width="43.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -780,7 +776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -791,7 +787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -802,7 +798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -813,7 +809,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -824,7 +820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -835,7 +831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -846,7 +842,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -857,7 +853,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -868,7 +864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -879,7 +875,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -890,7 +886,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -901,7 +897,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -912,7 +908,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -923,7 +919,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -934,7 +930,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -945,7 +941,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -956,7 +952,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -967,7 +963,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -978,7 +974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -989,7 +985,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1000,7 +996,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1011,7 +1007,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1022,7 +1018,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1033,312 +1029,312 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C42" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C44" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C45" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C46" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C48" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C49" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" t="s">
         <v>101</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>102</v>
       </c>
-      <c r="C51" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>103</v>
       </c>
-      <c r="B52" t="s">
-        <v>104</v>
-      </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
